--- a/docs/wip/Neutraal-Template-Niet-Functionele-Eisen.xlsx
+++ b/docs/wip/Neutraal-Template-Niet-Functionele-Eisen.xlsx
@@ -88,7 +88,7 @@
     <t>De applicatie voldoet aan de  WCAG2.2  succescriteria, niveau A en AA</t>
   </si>
   <si>
-    <t>WCAG2.1  is een wettelijke verplichting volgend uit  EN 301 549 .  WCAG2.2 voegt negen criteria toe ten opzichte van versie 2.1  ten opzichte van versie 2.1  en wordt  aangeraden  door het platform Digitale Overheid van het Ministerie van BZK voor nieuwe websites en applicaties. Zie de bijlage "WCAG2.2 successcriteria" voor een tabel met de succescriteria. Per succescriterium is aangegeven of Axe-core, en zo ja met welke regels, het criterium geautomatiseerd kan controleren.  {Geef aan of de succescriteria die Axe-core niet geautomatiseerd kan controleren wel of niet met de hand zullen worden gecontroleerd.}</t>
+    <t>WCAG2.1  is een wettelijke verplichting volgend uit  EN 301 549 .  WCAG2.2 voegt negen criteria toe ten opzichte van versie 2.1  ten opzichte van versie 2.1 en is  backwards compatible  met 2.1. Zie de bijlage  WCAG-succescriteria  voor een tabel met de succescriteria. Per succescriterium is aangegeven of Axe-core, en zo ja met welke regels, het criterium geautomatiseerd kan controleren.  {Geef aan of de succescriteria die Axe-core niet geautomatiseerd kan controleren wel of niet met de hand zullen worden gecontroleerd.}</t>
   </si>
   <si>
     <t>ICTU</t>
@@ -139,10 +139,10 @@
     <t>Security / 1</t>
   </si>
   <si>
-    <t>Voldoen aan de BIO- en SDD-maatregelen ten aanzien van informatiebeveiliging</t>
-  </si>
-  <si>
-    <t>BIO en SSD bevatten een aantal maatregelen ten aanzien van software en/of de infrastructurele componenten waar de software gebruik van maakt. Zie de bijlage "BIO- en SDD-maatregelen".</t>
+    <t>Voldoen aan de BIO- en SSD-maatregelen ten aanzien van informatiebeveiliging</t>
+  </si>
+  <si>
+    <t>BIO en SSD bevatten een aantal maatregelen ten aanzien van software en/of de infrastructurele componenten waar de software gebruik van maakt. Zie de bijlage  BIO- en SSD-maatregelen .</t>
   </si>
   <si>
     <t>{penetratietest en/of een secure code review} , te organiseren door  {ICTU of opdrachtgever}</t>
